--- a/artfynd/A 63635-2020 artfynd.xlsx
+++ b/artfynd/A 63635-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129428456</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129429290</v>
       </c>
       <c r="B5" t="n">
-        <v>92360</v>
+        <v>92363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,6 +1111,115 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129449442</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 63635, Lörstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>572810</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6406014</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Jan Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63635-2020 artfynd.xlsx
+++ b/artfynd/A 63635-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1221,6 +1221,116 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129454150</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91557</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A63635 Lörstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>572791</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6405983</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>flera fruktkroppar på granlåga</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63635-2020 artfynd.xlsx
+++ b/artfynd/A 63635-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129428456</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129429290</v>
       </c>
       <c r="B5" t="n">
-        <v>92363</v>
+        <v>92365</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>129454150</v>
       </c>
       <c r="B7" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 63635-2020 artfynd.xlsx
+++ b/artfynd/A 63635-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129428456</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129429290</v>
       </c>
       <c r="B5" t="n">
-        <v>92365</v>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>129454150</v>
       </c>
       <c r="B7" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 63635-2020 artfynd.xlsx
+++ b/artfynd/A 63635-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129428456</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129429290</v>
       </c>
       <c r="B5" t="n">
-        <v>92369</v>
+        <v>92370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>129454150</v>
       </c>
       <c r="B7" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 63635-2020 artfynd.xlsx
+++ b/artfynd/A 63635-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129428456</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129429290</v>
       </c>
       <c r="B5" t="n">
-        <v>92370</v>
+        <v>92373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>129454150</v>
       </c>
       <c r="B7" t="n">
-        <v>91564</v>
+        <v>91567</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 63635-2020 artfynd.xlsx
+++ b/artfynd/A 63635-2020 artfynd.xlsx
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson</t>
+          <t>Jan Aronsson, Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 63635-2020 artfynd.xlsx
+++ b/artfynd/A 63635-2020 artfynd.xlsx
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 63635-2020 artfynd.xlsx
+++ b/artfynd/A 63635-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129428456</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129428537</v>
       </c>
       <c r="B3" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129428528</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129429290</v>
       </c>
       <c r="B5" t="n">
-        <v>92373</v>
+        <v>92401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129449442</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>129454150</v>
       </c>
       <c r="B7" t="n">
-        <v>91567</v>
+        <v>91595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 63635-2020 artfynd.xlsx
+++ b/artfynd/A 63635-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129428456</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129428537</v>
       </c>
       <c r="B3" t="n">
-        <v>56911</v>
+        <v>56916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129428528</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129429290</v>
       </c>
       <c r="B5" t="n">
-        <v>92401</v>
+        <v>92407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129449442</v>
       </c>
       <c r="B6" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>129454150</v>
       </c>
       <c r="B7" t="n">
-        <v>91595</v>
+        <v>91601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 63635-2020 artfynd.xlsx
+++ b/artfynd/A 63635-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129428456</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129428537</v>
       </c>
       <c r="B3" t="n">
-        <v>56916</v>
+        <v>56917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>129428528</v>
       </c>
       <c r="B4" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129429290</v>
       </c>
       <c r="B5" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>129449442</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>129454150</v>
       </c>
       <c r="B7" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson</t>
+          <t>Jan Aronsson, Magnus Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 63635-2020 artfynd.xlsx
+++ b/artfynd/A 63635-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129428456</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129429290</v>
       </c>
       <c r="B5" t="n">
-        <v>92408</v>
+        <v>92413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>129454150</v>
       </c>
       <c r="B7" t="n">
-        <v>91602</v>
+        <v>91607</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Aronsson, Magnus Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand, Jan Aronsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 63635-2020 artfynd.xlsx
+++ b/artfynd/A 63635-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129428456</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>129429290</v>
       </c>
       <c r="B5" t="n">
-        <v>92413</v>
+        <v>92417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>129454150</v>
       </c>
       <c r="B7" t="n">
-        <v>91607</v>
+        <v>91611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
